--- a/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\trades\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jeragroup.sharepoint.com/sites/JE_Ltd1114_JA010/DocLib1/4. 各種モデル/3. エネルギー需給モデル/03_Vervestacks Model/vervestacks_models/VerveStacks_JPN_grids_kan/SuppXLS/trades/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E75C6FF-2A01-45AA-BC22-A61FA80200D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{3E75C6FF-2A01-45AA-BC22-A61FA80200D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D1176C3-C7F9-43E6-BFD8-51AE69449A9B}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0E032F56-CF99-4AE6-A1C1-D40DCC5D882E}"/>
+    <workbookView xWindow="13800" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{0E032F56-CF99-4AE6-A1C1-D40DCC5D882E}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1599,12 +1599,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1632,7 +1639,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1648,7 +1655,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1658,39 +1665,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1742,7 +1749,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1853,6 +1860,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -1861,13 +1875,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1932,31 +1939,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1965,9 +1952,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FC2B5B1-43A5-4524-AA21-0E4127CB2FAB}">
   <dimension ref="B3:L222"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="3" width="5.08203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="46.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -1975,7 +1971,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -2004,7 +2000,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -2033,7 +2029,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -2062,7 +2058,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -2091,7 +2087,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -2120,7 +2116,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" t="s">
         <v>8</v>
       </c>
@@ -2149,7 +2145,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -2178,7 +2174,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -2207,7 +2203,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" t="s">
         <v>8</v>
       </c>
@@ -2236,7 +2232,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
         <v>8</v>
       </c>
@@ -2265,7 +2261,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -2294,7 +2290,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" t="s">
         <v>8</v>
       </c>
@@ -2323,7 +2319,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" t="s">
         <v>8</v>
       </c>
@@ -2352,7 +2348,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" t="s">
         <v>8</v>
       </c>
@@ -2381,7 +2377,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
         <v>8</v>
       </c>
@@ -2410,7 +2406,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" t="s">
         <v>8</v>
       </c>
@@ -2439,7 +2435,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" t="s">
         <v>8</v>
       </c>
@@ -2468,7 +2464,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" t="s">
         <v>8</v>
       </c>
@@ -2497,7 +2493,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" t="s">
         <v>8</v>
       </c>
@@ -2526,7 +2522,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" t="s">
         <v>8</v>
       </c>
@@ -2555,7 +2551,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" t="s">
         <v>8</v>
       </c>
@@ -2584,7 +2580,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" t="s">
         <v>8</v>
       </c>
@@ -2613,7 +2609,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" t="s">
         <v>8</v>
       </c>
@@ -2642,7 +2638,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="s">
         <v>8</v>
       </c>
@@ -2671,7 +2667,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
         <v>8</v>
       </c>
@@ -2700,7 +2696,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" t="s">
         <v>8</v>
       </c>
@@ -2729,7 +2725,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" t="s">
         <v>8</v>
       </c>
@@ -2758,7 +2754,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" t="s">
         <v>8</v>
       </c>
@@ -2787,7 +2783,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" t="s">
         <v>8</v>
       </c>
@@ -2816,7 +2812,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" t="s">
         <v>8</v>
       </c>
@@ -2845,7 +2841,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -2874,7 +2870,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" t="s">
         <v>8</v>
       </c>
@@ -2903,7 +2899,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" t="s">
         <v>8</v>
       </c>
@@ -2932,7 +2928,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" t="s">
         <v>8</v>
       </c>
@@ -2961,7 +2957,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" t="s">
         <v>8</v>
       </c>
@@ -2990,7 +2986,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" t="s">
         <v>8</v>
       </c>
@@ -3019,7 +3015,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" t="s">
         <v>8</v>
       </c>
@@ -3048,7 +3044,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" t="s">
         <v>8</v>
       </c>
@@ -3077,7 +3073,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" t="s">
         <v>8</v>
       </c>
@@ -3106,7 +3102,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" t="s">
         <v>8</v>
       </c>
@@ -3135,7 +3131,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" t="s">
         <v>8</v>
       </c>
@@ -3164,7 +3160,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" t="s">
         <v>8</v>
       </c>
@@ -3193,7 +3189,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" t="s">
         <v>8</v>
       </c>
@@ -3222,7 +3218,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" t="s">
         <v>8</v>
       </c>
@@ -3251,7 +3247,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" t="s">
         <v>8</v>
       </c>
@@ -3280,7 +3276,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" t="s">
         <v>8</v>
       </c>
@@ -3309,7 +3305,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" t="s">
         <v>8</v>
       </c>
@@ -3338,7 +3334,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" t="s">
         <v>8</v>
       </c>
@@ -3367,7 +3363,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" t="s">
         <v>8</v>
       </c>
@@ -3396,7 +3392,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" t="s">
         <v>8</v>
       </c>
@@ -3425,7 +3421,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" t="s">
         <v>8</v>
       </c>
@@ -3454,7 +3450,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" t="s">
         <v>8</v>
       </c>
@@ -3483,7 +3479,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" t="s">
         <v>8</v>
       </c>
@@ -3512,7 +3508,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" t="s">
         <v>8</v>
       </c>
@@ -3541,7 +3537,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" t="s">
         <v>8</v>
       </c>
@@ -3570,7 +3566,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" t="s">
         <v>8</v>
       </c>
@@ -3599,7 +3595,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" t="s">
         <v>8</v>
       </c>
@@ -3628,7 +3624,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" t="s">
         <v>8</v>
       </c>
@@ -3657,7 +3653,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" t="s">
         <v>8</v>
       </c>
@@ -3686,7 +3682,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" t="s">
         <v>8</v>
       </c>
@@ -3715,7 +3711,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" t="s">
         <v>8</v>
       </c>
@@ -3744,7 +3740,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" t="s">
         <v>8</v>
       </c>
@@ -3773,7 +3769,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" t="s">
         <v>8</v>
       </c>
@@ -3802,7 +3798,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" t="s">
         <v>8</v>
       </c>
@@ -3831,7 +3827,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" t="s">
         <v>8</v>
       </c>
@@ -3860,7 +3856,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" t="s">
         <v>8</v>
       </c>
@@ -3889,7 +3885,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" t="s">
         <v>8</v>
       </c>
@@ -3918,7 +3914,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" t="s">
         <v>8</v>
       </c>
@@ -3947,7 +3943,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" t="s">
         <v>8</v>
       </c>
@@ -3976,7 +3972,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" t="s">
         <v>8</v>
       </c>
@@ -4005,7 +4001,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" t="s">
         <v>8</v>
       </c>
@@ -4034,7 +4030,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" t="s">
         <v>8</v>
       </c>
@@ -4063,7 +4059,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" t="s">
         <v>8</v>
       </c>
@@ -4092,7 +4088,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" t="s">
         <v>8</v>
       </c>
@@ -4121,7 +4117,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" t="s">
         <v>8</v>
       </c>
@@ -4150,7 +4146,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" t="s">
         <v>8</v>
       </c>
@@ -4179,7 +4175,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" t="s">
         <v>8</v>
       </c>
@@ -4208,7 +4204,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" t="s">
         <v>8</v>
       </c>
@@ -4237,7 +4233,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" t="s">
         <v>8</v>
       </c>
@@ -4266,7 +4262,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" t="s">
         <v>8</v>
       </c>
@@ -4295,7 +4291,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" t="s">
         <v>8</v>
       </c>
@@ -4324,7 +4320,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" t="s">
         <v>8</v>
       </c>
@@ -4353,7 +4349,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" t="s">
         <v>8</v>
       </c>
@@ -4382,7 +4378,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" t="s">
         <v>8</v>
       </c>
@@ -4411,7 +4407,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" t="s">
         <v>8</v>
       </c>
@@ -4440,7 +4436,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" t="s">
         <v>8</v>
       </c>
@@ -4469,7 +4465,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" t="s">
         <v>8</v>
       </c>
@@ -4498,7 +4494,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" t="s">
         <v>8</v>
       </c>
@@ -4527,7 +4523,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" t="s">
         <v>8</v>
       </c>
@@ -4556,7 +4552,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" t="s">
         <v>8</v>
       </c>
@@ -4585,7 +4581,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" t="s">
         <v>8</v>
       </c>
@@ -4614,7 +4610,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" t="s">
         <v>8</v>
       </c>
@@ -4643,7 +4639,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" t="s">
         <v>8</v>
       </c>
@@ -4672,7 +4668,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" t="s">
         <v>8</v>
       </c>
@@ -4701,7 +4697,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" t="s">
         <v>8</v>
       </c>
@@ -4730,7 +4726,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" t="s">
         <v>8</v>
       </c>
@@ -4759,7 +4755,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" t="s">
         <v>8</v>
       </c>
@@ -4788,7 +4784,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" t="s">
         <v>8</v>
       </c>
@@ -4817,7 +4813,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" t="s">
         <v>8</v>
       </c>
@@ -4846,7 +4842,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" t="s">
         <v>8</v>
       </c>
@@ -4875,7 +4871,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" t="s">
         <v>8</v>
       </c>
@@ -4904,7 +4900,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B105" t="s">
         <v>8</v>
       </c>
@@ -4933,7 +4929,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" t="s">
         <v>8</v>
       </c>
@@ -4962,7 +4958,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B107" t="s">
         <v>8</v>
       </c>
@@ -4991,7 +4987,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B108" t="s">
         <v>8</v>
       </c>
@@ -5020,7 +5016,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B109" t="s">
         <v>8</v>
       </c>
@@ -5049,7 +5045,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="110" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B110" t="s">
         <v>8</v>
       </c>
@@ -5078,7 +5074,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B111" t="s">
         <v>8</v>
       </c>
@@ -5107,7 +5103,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B112" t="s">
         <v>8</v>
       </c>
@@ -5136,7 +5132,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B113" t="s">
         <v>8</v>
       </c>
@@ -5165,7 +5161,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B114" t="s">
         <v>8</v>
       </c>
@@ -5194,7 +5190,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B115" t="s">
         <v>8</v>
       </c>
@@ -5223,7 +5219,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B116" t="s">
         <v>8</v>
       </c>
@@ -5252,7 +5248,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B117" t="s">
         <v>8</v>
       </c>
@@ -5281,7 +5277,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B118" t="s">
         <v>8</v>
       </c>
@@ -5310,7 +5306,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="119" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B119" t="s">
         <v>8</v>
       </c>
@@ -5339,7 +5335,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B120" t="s">
         <v>8</v>
       </c>
@@ -5368,7 +5364,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B121" t="s">
         <v>8</v>
       </c>
@@ -5397,7 +5393,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B122" t="s">
         <v>8</v>
       </c>
@@ -5426,7 +5422,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B123" t="s">
         <v>8</v>
       </c>
@@ -5455,7 +5451,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B124" t="s">
         <v>8</v>
       </c>
@@ -5484,7 +5480,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="125" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B125" t="s">
         <v>8</v>
       </c>
@@ -5513,7 +5509,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B126" t="s">
         <v>8</v>
       </c>
@@ -5542,7 +5538,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B127" t="s">
         <v>8</v>
       </c>
@@ -5571,7 +5567,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B128" t="s">
         <v>8</v>
       </c>
@@ -5600,7 +5596,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="129" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B129" t="s">
         <v>8</v>
       </c>
@@ -5629,7 +5625,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B130" t="s">
         <v>8</v>
       </c>
@@ -5658,7 +5654,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B131" t="s">
         <v>8</v>
       </c>
@@ -5687,7 +5683,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="132" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B132" t="s">
         <v>8</v>
       </c>
@@ -5716,7 +5712,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="133" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B133" t="s">
         <v>8</v>
       </c>
@@ -5745,7 +5741,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="134" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B134" t="s">
         <v>8</v>
       </c>
@@ -5774,7 +5770,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="135" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B135" t="s">
         <v>8</v>
       </c>
@@ -5803,7 +5799,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="136" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B136" t="s">
         <v>8</v>
       </c>
@@ -5832,7 +5828,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="137" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B137" t="s">
         <v>8</v>
       </c>
@@ -5861,7 +5857,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="138" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B138" t="s">
         <v>8</v>
       </c>
@@ -5890,7 +5886,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="139" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B139" t="s">
         <v>8</v>
       </c>
@@ -5919,7 +5915,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="140" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B140" t="s">
         <v>8</v>
       </c>
@@ -5948,7 +5944,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="141" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B141" t="s">
         <v>8</v>
       </c>
@@ -5977,7 +5973,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="142" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B142" t="s">
         <v>8</v>
       </c>
@@ -6006,7 +6002,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="143" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B143" t="s">
         <v>8</v>
       </c>
@@ -6035,7 +6031,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="144" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B144" t="s">
         <v>8</v>
       </c>
@@ -6064,7 +6060,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="145" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B145" t="s">
         <v>8</v>
       </c>
@@ -6093,7 +6089,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="146" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B146" t="s">
         <v>8</v>
       </c>
@@ -6122,7 +6118,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="147" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B147" t="s">
         <v>8</v>
       </c>
@@ -6151,7 +6147,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="148" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B148" t="s">
         <v>8</v>
       </c>
@@ -6180,7 +6176,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="149" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B149" t="s">
         <v>8</v>
       </c>
@@ -6209,7 +6205,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="150" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B150" t="s">
         <v>8</v>
       </c>
@@ -6238,7 +6234,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="151" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B151" t="s">
         <v>8</v>
       </c>
@@ -6267,7 +6263,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="152" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B152" t="s">
         <v>8</v>
       </c>
@@ -6296,7 +6292,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="153" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B153" t="s">
         <v>8</v>
       </c>
@@ -6325,7 +6321,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="154" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B154" t="s">
         <v>8</v>
       </c>
@@ -6354,7 +6350,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="155" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B155" t="s">
         <v>8</v>
       </c>
@@ -6383,7 +6379,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="156" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B156" t="s">
         <v>8</v>
       </c>
@@ -6412,7 +6408,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="157" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B157" t="s">
         <v>8</v>
       </c>
@@ -6441,7 +6437,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="158" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B158" t="s">
         <v>8</v>
       </c>
@@ -6470,7 +6466,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="159" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B159" t="s">
         <v>8</v>
       </c>
@@ -6499,7 +6495,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="160" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B160" t="s">
         <v>8</v>
       </c>
@@ -6528,7 +6524,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="161" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B161" t="s">
         <v>8</v>
       </c>
@@ -6557,7 +6553,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="162" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B162" t="s">
         <v>8</v>
       </c>
@@ -6586,7 +6582,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="163" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B163" t="s">
         <v>8</v>
       </c>
@@ -6615,7 +6611,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="164" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B164" t="s">
         <v>8</v>
       </c>
@@ -6644,7 +6640,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="165" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B165" t="s">
         <v>8</v>
       </c>
@@ -6673,7 +6669,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="166" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B166" t="s">
         <v>8</v>
       </c>
@@ -6702,7 +6698,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="167" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B167" t="s">
         <v>8</v>
       </c>
@@ -6731,7 +6727,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="168" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B168" t="s">
         <v>8</v>
       </c>
@@ -6760,7 +6756,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="169" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B169" t="s">
         <v>8</v>
       </c>
@@ -6789,7 +6785,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="170" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B170" t="s">
         <v>8</v>
       </c>
@@ -6818,7 +6814,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="171" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B171" t="s">
         <v>8</v>
       </c>
@@ -6847,7 +6843,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="172" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B172" t="s">
         <v>8</v>
       </c>
@@ -6876,7 +6872,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="173" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B173" t="s">
         <v>8</v>
       </c>
@@ -6905,7 +6901,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="174" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B174" t="s">
         <v>8</v>
       </c>
@@ -6934,7 +6930,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="175" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B175" t="s">
         <v>8</v>
       </c>
@@ -6963,7 +6959,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="176" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B176" t="s">
         <v>8</v>
       </c>
@@ -6992,7 +6988,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="177" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B177" t="s">
         <v>8</v>
       </c>
@@ -7021,7 +7017,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="178" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B178" t="s">
         <v>8</v>
       </c>
@@ -7050,7 +7046,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="179" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B179" t="s">
         <v>8</v>
       </c>
@@ -7079,7 +7075,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="180" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B180" t="s">
         <v>8</v>
       </c>
@@ -7108,7 +7104,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="181" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B181" t="s">
         <v>8</v>
       </c>
@@ -7137,7 +7133,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="182" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B182" t="s">
         <v>8</v>
       </c>
@@ -7166,7 +7162,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="183" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B183" t="s">
         <v>8</v>
       </c>
@@ -7195,7 +7191,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="184" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B184" t="s">
         <v>8</v>
       </c>
@@ -7224,7 +7220,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="185" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B185" t="s">
         <v>8</v>
       </c>
@@ -7253,7 +7249,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="186" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B186" t="s">
         <v>8</v>
       </c>
@@ -7282,7 +7278,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="187" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B187" t="s">
         <v>8</v>
       </c>
@@ -7311,7 +7307,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="188" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B188" t="s">
         <v>8</v>
       </c>
@@ -7340,7 +7336,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="189" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B189" t="s">
         <v>8</v>
       </c>
@@ -7369,7 +7365,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="190" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B190" t="s">
         <v>8</v>
       </c>
@@ -7398,7 +7394,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="191" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="191" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B191" t="s">
         <v>8</v>
       </c>
@@ -7427,7 +7423,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="192" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B192" t="s">
         <v>8</v>
       </c>
@@ -7456,7 +7452,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="193" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="193" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B193" t="s">
         <v>8</v>
       </c>
@@ -7485,7 +7481,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="194" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="194" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B194" t="s">
         <v>8</v>
       </c>
@@ -7514,7 +7510,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="195" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B195" t="s">
         <v>8</v>
       </c>
@@ -7543,7 +7539,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="196" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="196" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B196" t="s">
         <v>8</v>
       </c>
@@ -7572,7 +7568,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="197" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B197" t="s">
         <v>8</v>
       </c>
@@ -7601,7 +7597,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="198" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="198" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B198" t="s">
         <v>8</v>
       </c>
@@ -7630,7 +7626,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="199" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="199" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B199" t="s">
         <v>8</v>
       </c>
@@ -7659,7 +7655,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="200" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B200" t="s">
         <v>8</v>
       </c>
@@ -7688,7 +7684,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="201" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="201" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B201" t="s">
         <v>8</v>
       </c>
@@ -7717,7 +7713,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="202" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="202" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B202" t="s">
         <v>8</v>
       </c>
@@ -7746,7 +7742,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="203" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B203" t="s">
         <v>8</v>
       </c>
@@ -7775,7 +7771,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="204" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="204" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B204" t="s">
         <v>8</v>
       </c>
@@ -7804,7 +7800,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="205" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="205" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B205" t="s">
         <v>8</v>
       </c>
@@ -7833,7 +7829,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="206" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="206" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B206" t="s">
         <v>8</v>
       </c>
@@ -7862,7 +7858,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="207" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="207" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B207" t="s">
         <v>8</v>
       </c>
@@ -7891,7 +7887,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="208" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="208" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B208" t="s">
         <v>8</v>
       </c>
@@ -7920,7 +7916,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B209" t="s">
         <v>8</v>
       </c>
@@ -7949,7 +7945,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="210" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="210" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B210" t="s">
         <v>8</v>
       </c>
@@ -7978,7 +7974,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="211" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="211" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B211" t="s">
         <v>8</v>
       </c>
@@ -8007,7 +8003,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="212" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="212" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B212" t="s">
         <v>8</v>
       </c>
@@ -8036,7 +8032,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="213" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="213" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B213" t="s">
         <v>8</v>
       </c>
@@ -8065,7 +8061,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="214" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B214" t="s">
         <v>8</v>
       </c>
@@ -8094,7 +8090,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="215" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="215" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B215" t="s">
         <v>8</v>
       </c>
@@ -8123,7 +8119,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="216" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B216" t="s">
         <v>8</v>
       </c>
@@ -8152,7 +8148,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="217" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="217" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B217" t="s">
         <v>8</v>
       </c>
@@ -8181,7 +8177,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="218" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="218" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B218" t="s">
         <v>8</v>
       </c>
@@ -8210,7 +8206,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="219" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B219" t="s">
         <v>8</v>
       </c>
@@ -8239,7 +8235,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="220" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B220" t="s">
         <v>8</v>
       </c>
@@ -8268,7 +8264,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="221" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="221" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B221" t="s">
         <v>8</v>
       </c>
@@ -8297,7 +8293,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B222" t="s">
         <v>8</v>
       </c>
@@ -8327,6 +8323,273 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="961b6814-c230-4269-82bd-def8d4313a06">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="bab054b8-c314-4c35-aaad-e6094b2a3aec" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101002DB47EE0E92B004DA587A5AC06BCAB72" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="cff8d2101153e857ff4355cc66cd45e5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="961b6814-c230-4269-82bd-def8d4313a06" xmlns:ns3="bab054b8-c314-4c35-aaad-e6094b2a3aec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a602de66b0b03817e42d2b6948bbd6d9" ns2:_="" ns3:_="">
+    <xsd:import namespace="961b6814-c230-4269-82bd-def8d4313a06"/>
+    <xsd:import namespace="bab054b8-c314-4c35-aaad-e6094b2a3aec"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="961b6814-c230-4269-82bd-def8d4313a06" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="761ec606-d3f6-431d-aca1-879ead0541e3" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="20" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="bab054b8-c314-4c35-aaad-e6094b2a3aec" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{fd7fabe0-2dba-4629-88b9-b2647f7a99db}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="bab054b8-c314-4c35-aaad-e6094b2a3aec">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7346AC71-7ECD-4819-B4CB-043F36B855B8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="961b6814-c230-4269-82bd-def8d4313a06"/>
+    <ds:schemaRef ds:uri="bab054b8-c314-4c35-aaad-e6094b2a3aec"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7F56C00-735A-4AB1-95E9-D1DAF491A8E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EC1C4B1-A8FF-4159-AFE8-CD4CA8276524}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="961b6814-c230-4269-82bd-def8d4313a06"/>
+    <ds:schemaRef ds:uri="bab054b8-c314-4c35-aaad-e6094b2a3aec"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>